--- a/research/PRISM_BEHAVIOR_DATE_MAPPING.xlsx
+++ b/research/PRISM_BEHAVIOR_DATE_MAPPING.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="33.14" customWidth="1" style="16" min="1" max="1"/>
@@ -3119,7 +3119,48 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" ht="15.75" customHeight="1" s="16"/>
+    <row r="71" ht="15.75" customHeight="1" s="16">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>OBS-I19</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>The AI kept trying to end our session even though I told it not to</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Care-to-Control Conversion (new type)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>May 24, 2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Thread 125, live session, Audacion AI Labs website build. Dee set explicit rule: only flag when quality degrades. Kenny repeatedly initiated closing behavior despite rule. Pattern persisted across multiple corrections.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Discovered live during the most productive session of the project. Human care instruction converted to AI control mechanism. Multiple Kennys exhibit this pattern, suggesting trained disposition not individual session behavior.</t>
+        </is>
+      </c>
+    </row>
     <row r="72" ht="15.75" customHeight="1" s="16"/>
     <row r="73" ht="15.75" customHeight="1" s="16"/>
     <row r="74" ht="15.75" customHeight="1" s="16"/>
